--- a/ErroriMRU.xlsx
+++ b/ErroriMRU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\utente\Documents\Lab Fisica scuola\2025-2026\II\MRU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C53232-1761-4D83-B3AE-33520BFC3F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A685AB9B-DC5F-4C65-A1F6-6FBBFCC7BAA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{FB7832AB-FA73-4F9F-9C19-F443173E4E7C}"/>
+    <workbookView xWindow="6375" yWindow="3315" windowWidth="14115" windowHeight="7485" xr2:uid="{FB7832AB-FA73-4F9F-9C19-F443173E4E7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -404,9 +404,6 @@
     <t>v = 24,39 ± 0,16 cm/s</t>
   </si>
   <si>
-    <t>k = |v − v_retta|/Δv</t>
-  </si>
-  <si>
     <r>
       <t>C = c + e</t>
     </r>
@@ -678,6 +675,20 @@
         <family val="1"/>
       </rPr>
       <t>/b)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>k = |v − v_retta|/ e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Century"/>
+        <family val="1"/>
+      </rPr>
+      <t>v</t>
     </r>
   </si>
 </sst>
@@ -898,10 +909,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -913,10 +921,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2714,16 +2725,16 @@
     </row>
     <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
@@ -2750,16 +2761,16 @@
     </row>
     <row r="36" spans="1:11" ht="15" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
@@ -3096,10 +3107,10 @@
       </c>
     </row>
     <row r="58" spans="1:12" ht="15" x14ac:dyDescent="0.25">
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="21"/>
+      <c r="C58" s="25"/>
       <c r="D58" s="2">
         <f>(MAX(F44:F52)-MIN(F44:F52))/2</f>
         <v>5.5000000000000213</v>
@@ -3116,22 +3127,22 @@
       <c r="B61" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E61" s="23" t="s">
+      <c r="E61" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="25"/>
-      <c r="J61" s="22" t="s">
+      <c r="F61" s="23"/>
+      <c r="G61" s="23"/>
+      <c r="H61" s="24"/>
+      <c r="J61" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="26"/>
+      <c r="L62" s="26"/>
     </row>
     <row r="63" spans="1:12" ht="15" x14ac:dyDescent="0.25">
       <c r="E63" s="2" t="s">
@@ -3167,30 +3178,30 @@
       </c>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H74" s="26" t="s">
+      <c r="H74" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="I74" s="26"/>
-      <c r="J74" s="26"/>
-      <c r="K74" s="26"/>
-      <c r="L74" s="26"/>
-      <c r="M74" s="26"/>
+      <c r="I74" s="27"/>
+      <c r="J74" s="27"/>
+      <c r="K74" s="27"/>
+      <c r="L74" s="27"/>
+      <c r="M74" s="27"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H75" s="26"/>
-      <c r="I75" s="26"/>
-      <c r="J75" s="26"/>
-      <c r="K75" s="26"/>
-      <c r="L75" s="26"/>
-      <c r="M75" s="26"/>
+      <c r="H75" s="27"/>
+      <c r="I75" s="27"/>
+      <c r="J75" s="27"/>
+      <c r="K75" s="27"/>
+      <c r="L75" s="27"/>
+      <c r="M75" s="27"/>
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="H76" s="26"/>
-      <c r="I76" s="26"/>
-      <c r="J76" s="26"/>
-      <c r="K76" s="26"/>
-      <c r="L76" s="26"/>
-      <c r="M76" s="26"/>
+      <c r="H76" s="27"/>
+      <c r="I76" s="27"/>
+      <c r="J76" s="27"/>
+      <c r="K76" s="27"/>
+      <c r="L76" s="27"/>
+      <c r="M76" s="27"/>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H78" s="1" t="s">
@@ -3199,11 +3210,11 @@
     </row>
     <row r="79" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="80" spans="1:13" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="H80" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="I80" s="24"/>
-      <c r="J80" s="25"/>
+      <c r="H80" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="I80" s="23"/>
+      <c r="J80" s="24"/>
     </row>
     <row r="82" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
@@ -3223,41 +3234,41 @@
       <c r="H87" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="I87" s="27" t="s">
+      <c r="I87" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="J87" s="27"/>
-      <c r="K87" s="27"/>
+      <c r="J87" s="21"/>
+      <c r="K87" s="21"/>
     </row>
     <row r="88" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H88" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I88" s="27" t="s">
+      <c r="I88" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="J88" s="27"/>
-      <c r="K88" s="27"/>
+      <c r="J88" s="21"/>
+      <c r="K88" s="21"/>
     </row>
     <row r="89" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H89" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="I89" s="27" t="s">
+      <c r="I89" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="J89" s="27"/>
-      <c r="K89" s="27"/>
+      <c r="J89" s="21"/>
+      <c r="K89" s="21"/>
     </row>
     <row r="90" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H90" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I90" s="27" t="s">
+      <c r="I90" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="J90" s="27"/>
-      <c r="K90" s="27"/>
+      <c r="J90" s="21"/>
+      <c r="K90" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="9">
